--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Revenue'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Personnel'!$A1:$N4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Personnel'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Operating Expenses'!$A1:$N7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Operating Expenses'!$A1:$N8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'P&amp;L Summary'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'P&amp;L Summary'!$1:$1</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="48">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Insurance</t>
+  </si>
+  <si>
+    <t>Compliance Contract</t>
   </si>
   <si>
     <t>Curriculum &amp; Materials</t>
@@ -1333,7 +1336,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1525,34 +1528,34 @@
         <v>38</v>
       </c>
       <c r="B5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="C5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="F5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="G5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="H5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="I5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="J5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="K5" s="10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="L5" s="10">
         <v>0</v>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="N5" s="10">
         <f>SUM(B5:M5)</f>
-        <v>5000</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1570,34 +1573,34 @@
         <v>39</v>
       </c>
       <c r="B6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="C6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="D6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="E6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="F6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="G6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="H6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="I6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="J6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="K6" s="10">
-        <v>313</v>
+        <v>500</v>
       </c>
       <c r="L6" s="10">
         <v>0</v>
@@ -1607,63 +1610,108 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="10">
+        <v>313</v>
+      </c>
+      <c r="C7" s="10">
+        <v>313</v>
+      </c>
+      <c r="D7" s="10">
+        <v>313</v>
+      </c>
+      <c r="E7" s="10">
+        <v>313</v>
+      </c>
+      <c r="F7" s="10">
+        <v>313</v>
+      </c>
+      <c r="G7" s="10">
+        <v>313</v>
+      </c>
+      <c r="H7" s="10">
+        <v>313</v>
+      </c>
+      <c r="I7" s="10">
+        <v>313</v>
+      </c>
+      <c r="J7" s="10">
+        <v>313</v>
+      </c>
+      <c r="K7" s="10">
+        <v>313</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <f>SUM(B7:M7)</f>
         <v>3125</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="11" t="str">
-        <f>SUM(B2:B6)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="str">
-        <f>SUM(C2:C6)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="str">
-        <f>SUM(D2:D6)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="11" t="str">
-        <f>SUM(E2:E6)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="11" t="str">
-        <f>SUM(F2:F6)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="11" t="str">
-        <f>SUM(G2:G6)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="11" t="str">
-        <f>SUM(H2:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="11" t="str">
-        <f>SUM(I2:I6)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="11" t="str">
-        <f>SUM(J2:J6)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="11" t="str">
-        <f>SUM(K2:K6)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="str">
-        <f>SUM(L2:L6)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="str">
-        <f>SUM(M2:M6)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="11" t="str">
-        <f>SUM(B7:M7)</f>
+    <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="11" t="str">
+        <f>SUM(B2:B7)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="str">
+        <f>SUM(C2:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f>SUM(D2:D7)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f>SUM(E2:E7)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="str">
+        <f>SUM(F2:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="str">
+        <f>SUM(G2:G7)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="str">
+        <f>SUM(H2:H7)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="str">
+        <f>SUM(I2:I7)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="11" t="str">
+        <f>SUM(J2:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="11" t="str">
+        <f>SUM(K2:K7)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="11" t="str">
+        <f>SUM(L2:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="str">
+        <f>SUM(M2:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="str">
+        <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
     </row>
@@ -1736,7 +1784,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="13">
         <f>Revenue!B7</f>
@@ -1793,7 +1841,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="10">
         <f>Personnel!B4</f>
@@ -1850,64 +1898,64 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="10">
-        <f>'Operating Expenses'!B7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!B8</f>
+        <v>3338</v>
       </c>
       <c r="C4" s="10">
-        <f>'Operating Expenses'!C7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!C8</f>
+        <v>3338</v>
       </c>
       <c r="D4" s="10">
-        <f>'Operating Expenses'!D7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!D8</f>
+        <v>3338</v>
       </c>
       <c r="E4" s="10">
-        <f>'Operating Expenses'!E7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!E8</f>
+        <v>3338</v>
       </c>
       <c r="F4" s="10">
-        <f>'Operating Expenses'!F7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!F8</f>
+        <v>3338</v>
       </c>
       <c r="G4" s="10">
-        <f>'Operating Expenses'!G7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!G8</f>
+        <v>3338</v>
       </c>
       <c r="H4" s="10">
-        <f>'Operating Expenses'!H7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!H8</f>
+        <v>3338</v>
       </c>
       <c r="I4" s="10">
-        <f>'Operating Expenses'!I7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!I8</f>
+        <v>3338</v>
       </c>
       <c r="J4" s="10">
-        <f>'Operating Expenses'!J7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!J8</f>
+        <v>3338</v>
       </c>
       <c r="K4" s="10">
-        <f>'Operating Expenses'!K7</f>
-        <v>2963</v>
+        <f>'Operating Expenses'!K8</f>
+        <v>3338</v>
       </c>
       <c r="L4" s="10" t="str">
-        <f>'Operating Expenses'!L7</f>
+        <f>'Operating Expenses'!L8</f>
         <v>0</v>
       </c>
       <c r="M4" s="10" t="str">
-        <f>'Operating Expenses'!M7</f>
+        <f>'Operating Expenses'!M8</f>
         <v>0</v>
       </c>
       <c r="N4" s="10">
         <f>SUM(B4:M4)</f>
-        <v>29625</v>
+        <v>33375</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="10">
         <v>0</v>
@@ -1952,7 +2000,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>SUM(B3:B5)</f>
@@ -2004,12 +2052,12 @@
       </c>
       <c r="N6" s="14">
         <f>SUM(B6:M6)</f>
-        <v>94141</v>
+        <v>97891</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="15" t="str">
         <f>B2-B6</f>
@@ -2061,7 +2109,7 @@
       </c>
       <c r="N7" s="15">
         <f>N2-N6</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -9,6 +9,7 @@
     <sheet sheetId="3" name="Personnel" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Operating Expenses" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="P&amp;L Summary" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Decision History" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$E11</definedName>
@@ -21,13 +22,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'P&amp;L Summary'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'P&amp;L Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Decision History'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -171,6 +174,15 @@
   </si>
   <si>
     <t>Profit / (Loss)</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -182,7 +194,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -220,6 +232,24 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -316,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -335,6 +365,13 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2120,4 +2157,71 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BLiberty Learning Co-Op&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>